--- a/tiflow-xborder/develop/2.0.0-ballot.2/ValueSet-tiflow-xborder-operation-outcome-details-vs.xlsx
+++ b/tiflow-xborder/develop/2.0.0-ballot.2/ValueSet-tiflow-xborder-operation-outcome-details-vs.xlsx
@@ -26,7 +26,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/erp-eu/ValueSet/tiflow-xborder-operation-outcome-details-vs</t>
+    <t>https://gematik.de/fhir/tiflow-xborder/ValueSet/tiflow-xborder-operation-outcome-details-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -110,7 +110,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>https://gematik.de/fhir/erp-eu/CodeSystem/tiflow-xborder-operation-outcome-details-cs</t>
+    <t>https://gematik.de/fhir/tiflow-xborder/CodeSystem/tiflow-xborder-operation-outcome-details-cs</t>
   </si>
   <si>
     <t>Concept</t>
